--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486827_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486827_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.2614</v>
+        <v>12.8806</v>
       </c>
       <c r="E2" t="n">
-        <v>11.3546</v>
+        <v>11.5201</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9068</v>
+        <v>1.3605</v>
       </c>
       <c r="G2" t="n">
         <v>10.3272</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3085</v>
+        <v>-0.6893</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8834</v>
+        <v>-0.7178</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5748</v>
+        <v>0.0285</v>
       </c>
       <c r="V2" t="n">
         <v>3.0496</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0438</v>
+        <v>2.2065</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7862</v>
+        <v>2.0483</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2576</v>
+        <v>0.1583</v>
       </c>
       <c r="G3" t="n">
         <v>2.3857</v>
@@ -688,13 +688,13 @@
         <v>0.3862</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.728</v>
+        <v>-0.5653</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2484</v>
+        <v>0.0136</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4797</v>
+        <v>-0.579</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3915</v>
+        <v>1.1793</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3245</v>
+        <v>3.8144</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.9331</v>
+        <v>-2.6351</v>
       </c>
       <c r="G4" t="n">
         <v>1.3719</v>
@@ -766,13 +766,13 @@
         <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0774</v>
+        <v>-0.2896</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7718</v>
+        <v>0.2617</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8492</v>
+        <v>-0.5512</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4477</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6804</v>
+        <v>0.8887</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5919</v>
+        <v>-0.4333</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2723</v>
+        <v>1.3219</v>
       </c>
       <c r="G5" t="n">
         <v>0.377</v>
@@ -844,13 +844,13 @@
         <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9323</v>
+        <v>-0.724</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0209</v>
+        <v>-0.8623</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0886</v>
+        <v>0.1383</v>
       </c>
       <c r="V5" t="n">
         <v>0.6565</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2886</v>
+        <v>0.3245</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5861</v>
+        <v>-1.4758</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8748</v>
+        <v>1.8003</v>
       </c>
       <c r="G6" t="n">
         <v>1.1372</v>
@@ -922,13 +922,13 @@
         <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2425</v>
+        <v>-0.2066</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2484</v>
+        <v>-0.138</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0059</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.22</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0379</v>
+        <v>0.1221</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0052</v>
+        <v>-1.8948</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9672</v>
+        <v>2.0169</v>
       </c>
       <c r="G7" t="n">
         <v>0.3775</v>
@@ -1000,13 +1000,13 @@
         <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1875</v>
+        <v>-0.0275</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.607</v>
+        <v>-0.4966</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4195</v>
+        <v>0.4692</v>
       </c>
       <c r="V7" t="n">
         <v>0.3513</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7363</v>
+        <v>-1.3791</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7942</v>
+        <v>-1.6356</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0579</v>
+        <v>0.2565</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9121</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4193</v>
+        <v>-0.062</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4691</v>
+        <v>-0.3105</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0498</v>
+        <v>0.2485</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7912</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3396</v>
+        <v>-3.2403</v>
       </c>
       <c r="E9" t="n">
         <v>-2.6322</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7074</v>
+        <v>-0.608</v>
       </c>
       <c r="G9" t="n">
         <v>0.446</v>
@@ -1156,13 +1156,13 @@
         <v>1.7377</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.982</v>
+        <v>-0.8827</v>
       </c>
       <c r="T9" t="n">
         <v>-0.3591</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6229</v>
+        <v>-0.5236</v>
       </c>
       <c r="V9" t="n">
         <v>0.2856</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1849</v>
+        <v>-3.6208</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7574</v>
+        <v>-3.392</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4275</v>
+        <v>-0.2288</v>
       </c>
       <c r="G10" t="n">
         <v>-4.5822</v>
@@ -1234,13 +1234,13 @@
         <v>1.5446</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0813</v>
+        <v>-0.5172</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2693</v>
+        <v>-0.9039</v>
       </c>
       <c r="U10" t="n">
-        <v>0.188</v>
+        <v>0.3866</v>
       </c>
       <c r="V10" t="n">
         <v>0.8995</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7595</v>
+        <v>-6.9263</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.001</v>
+        <v>-4.9941</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7584</v>
+        <v>-1.9322</v>
       </c>
       <c r="G11" t="n">
         <v>-5.8952</v>
@@ -1312,13 +1312,13 @@
         <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8329</v>
+        <v>-0.9998</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3591</v>
+        <v>-0.3522</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4738</v>
+        <v>-0.6476</v>
       </c>
       <c r="V11" t="n">
         <v>1.5133</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.607500000000001</v>
+        <v>2.435200000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09729999999999617</v>
+        <v>0.9249999999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5102</v>
+        <v>1.5103</v>
       </c>
       <c r="G12" t="n">
         <v>5.033</v>
@@ -1390,13 +1390,13 @@
         <v>11.5845</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.791699999999999</v>
+        <v>-4.964</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.6929</v>
+        <v>-3.8651</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.099</v>
+        <v>-1.0989</v>
       </c>
       <c r="V12" t="n">
         <v>4.2969</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.335</v>
+        <v>2.5876</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3497</v>
+        <v>-0.2016</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9852</v>
+        <v>2.7892</v>
       </c>
       <c r="G13" t="n">
         <v>2.4319</v>
@@ -1468,13 +1468,13 @@
         <v>1.9308</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8025</v>
+        <v>1.0551</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7646</v>
+        <v>0.2133</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0378</v>
+        <v>0.8418</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8995</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6517</v>
+        <v>2.3579</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4864</v>
+        <v>1.6932</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1653</v>
+        <v>0.6646</v>
       </c>
       <c r="G14" t="n">
         <v>1.0582</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2925</v>
+        <v>0.4137</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0548</v>
+        <v>0.2617</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3473</v>
+        <v>0.152</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4655</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>A. NAVAS CERVERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1991</v>
+        <v>0.9629</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9648</v>
+        <v>-0.366</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2342</v>
+        <v>1.3289</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0407</v>
+        <v>-1.7424</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.269</v>
+        <v>0.7511</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3097</v>
+        <v>-2.4935</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0273</v>
+        <v>-0.1476</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5446</v>
+        <v>0.6141</v>
       </c>
       <c r="L15" t="n">
-        <v>0.572</v>
+        <v>-0.7617</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0134</v>
+        <v>-1.5948</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2756</v>
+        <v>0.137</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2623</v>
+        <v>-1.7318</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3862</v>
+        <v>2.3169</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3862</v>
+        <v>2.3169</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7722</v>
+        <v>0.2826</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9375</v>
+        <v>-0.5041</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1653</v>
+        <v>0.7866</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1057</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1799</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. DEL CASTILLO LEON</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1996</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6991000000000001</v>
+        <v>0.3443</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6191</v>
+        <v>0.0407</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.454</v>
+        <v>-0.269</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1651</v>
+        <v>0.3097</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9073</v>
+        <v>0.0273</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.5222</v>
+        <v>-0.5446</v>
       </c>
       <c r="L16" t="n">
-        <v>0.615</v>
+        <v>0.572</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7118</v>
+        <v>0.0134</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0682</v>
+        <v>0.2756</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.78</v>
+        <v>-0.2623</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6783</v>
+        <v>0.4275</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0545</v>
+        <v>0.317</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6239</v>
+        <v>0.1105</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3334</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.0845</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. NAVAS CERVERA</t>
+          <t>J. DEL CASTILLO LEON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5058</v>
+        <v>0.3141</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2968</v>
+        <v>-1.0093</v>
       </c>
       <c r="F17" t="n">
-        <v>0.791</v>
+        <v>1.3235</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7424</v>
+        <v>-1.6191</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7511</v>
+        <v>-1.454</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.4935</v>
+        <v>-0.1651</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1476</v>
+        <v>-0.9073</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6141</v>
+        <v>-1.5222</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7617</v>
+        <v>0.615</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5948</v>
+        <v>-0.7118</v>
       </c>
       <c r="N17" t="n">
-        <v>0.137</v>
+        <v>0.0682</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7318</v>
+        <v>-0.78</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3169</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3169</v>
+        <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1861</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4349</v>
+        <v>-0.2558</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2488</v>
+        <v>1.0486</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1057</v>
+        <v>1.3334</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2856</v>
+        <v>2.0845</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1799</v>
+        <v>-0.7511</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VERA PEIRO</t>
+          <t>J. HERRERO ALONSO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2714</v>
+        <v>-1.4576</v>
       </c>
       <c r="E18" t="n">
-        <v>2.82</v>
+        <v>-1.0562</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.0914</v>
+        <v>-0.4015</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8825</v>
+        <v>2.1615</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5937</v>
+        <v>3.0068</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4763</v>
+        <v>-0.8454</v>
       </c>
       <c r="J18" t="n">
-        <v>1.615</v>
+        <v>4.8457</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8011</v>
+        <v>2.5939</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8138</v>
+        <v>2.2518</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4975</v>
+        <v>-2.6843</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2074</v>
+        <v>0.4129</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2901</v>
+        <v>-3.0972</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>-4.827</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9654</v>
+        <v>1.9308</v>
       </c>
       <c r="S18" t="n">
-        <v>2.289</v>
+        <v>0.8756</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5992</v>
+        <v>-0.0902</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6898</v>
+        <v>0.9659</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.6779</v>
+        <v>-1.5985</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5712</v>
+        <v>-0.9847</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.2491</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1319</v>
+        <v>-1.5432</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3326</v>
+        <v>-1.6087</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2007</v>
+        <v>0.0654</v>
       </c>
       <c r="G19" t="n">
         <v>-4.803</v>
@@ -1936,13 +1936,13 @@
         <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2524</v>
+        <v>1.8411</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1936</v>
+        <v>0.5304</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4459</v>
+        <v>1.3107</v>
       </c>
       <c r="V19" t="n">
         <v>1.4187</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4581</v>
+        <v>-1.7575</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8157</v>
+        <v>-1.402</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6424</v>
+        <v>-0.3555</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6784</v>
@@ -2014,13 +2014,13 @@
         <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2318</v>
+        <v>0.4688</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6623</v>
+        <v>-0.2486</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4305</v>
+        <v>0.7174</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5133</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. HERRERO ALONSO</t>
+          <t>A. VERA PEIRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6257</v>
+        <v>-1.8574</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.987</v>
+        <v>2.0961</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6387</v>
+        <v>-3.9535</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1615</v>
+        <v>-0.8825</v>
       </c>
       <c r="H21" t="n">
-        <v>3.0068</v>
+        <v>0.5937</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8454</v>
+        <v>-1.4763</v>
       </c>
       <c r="J21" t="n">
-        <v>4.8457</v>
+        <v>1.615</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5939</v>
+        <v>0.8011</v>
       </c>
       <c r="L21" t="n">
-        <v>2.2518</v>
+        <v>0.8138</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6843</v>
+        <v>-2.4975</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4129</v>
+        <v>-0.2074</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.0972</v>
+        <v>-2.2901</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.827</v>
+        <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2924</v>
+        <v>1.703</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.021</v>
+        <v>0.8753</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7286</v>
+        <v>0.8277</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5985</v>
+        <v>-2.6779</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.9847</v>
+        <v>0.5712</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6138</v>
+        <v>-3.2491</v>
       </c>
     </row>
     <row r="22">
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.607500000000001</v>
+        <v>0.4610999999999994</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5103</v>
+        <v>-1.5102</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.09739999999999993</v>
+        <v>1.9711</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.033099999999999</v>
+        <v>-5.0331</v>
       </c>
       <c r="H22" t="n">
         <v>4.4843</v>
@@ -2170,22 +2170,22 @@
         <v>13.5155</v>
       </c>
       <c r="S22" t="n">
-        <v>5.7916</v>
+        <v>7.8602</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0988</v>
+        <v>1.099</v>
       </c>
       <c r="U22" t="n">
-        <v>4.6927</v>
+        <v>6.761200000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-4.296900000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>4.411999999999999</v>
+        <v>4.412</v>
       </c>
       <c r="X22" t="n">
-        <v>-8.708899999999998</v>
+        <v>-8.7089</v>
       </c>
     </row>
   </sheetData>
